--- a/experiment/coil_data/X.xlsx
+++ b/experiment/coil_data/X.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\allen\Desktop\Homework\Physics 108\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\allen\Desktop\Homework\Physics 108\Scope\github\experiment\coil_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02ADA8FC-A82B-4424-83D5-52A1CB6155DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEC50152-4D2D-4659-9BA0-B7A278CCFE83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{BD55E609-27D6-46B4-A2AF-887C5DEF06BC}"/>
   </bookViews>
@@ -515,7 +515,7 @@
         <v>2.5</v>
       </c>
       <c r="B9">
-        <v>3.43</v>
+        <v>34.299999999999997</v>
       </c>
       <c r="C9">
         <v>0.93100000000000005</v>
